--- a/list_categorized.xlsx
+++ b/list_categorized.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E526"/>
+  <dimension ref="A1:E558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="20.58203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -12165,7 +12165,7 @@
       </c>
       <c r="B466" s="5" t="inlineStr">
         <is>
-          <t>כללי</t>
+          <t>חיות מחמד</t>
         </is>
       </c>
       <c r="C466" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
         </is>
       </c>
       <c r="E466" s="6" t="n">
-        <v>12.9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="467">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B467" s="5" t="inlineStr">
         <is>
-          <t>כללי</t>
+          <t>חיות מחמד</t>
         </is>
       </c>
       <c r="C467" s="5" t="inlineStr">
@@ -12204,7 +12204,7 @@
         </is>
       </c>
       <c r="E467" s="6" t="n">
-        <v>12.9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="468">
@@ -12540,7 +12540,7 @@
       </c>
       <c r="B481" s="5" t="inlineStr">
         <is>
-          <t>כללי</t>
+          <t>חיות מחמד</t>
         </is>
       </c>
       <c r="C481" s="5" t="inlineStr">
@@ -12554,7 +12554,7 @@
         </is>
       </c>
       <c r="E481" s="6" t="n">
-        <v>12.9</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="482">
@@ -13680,6 +13680,806 @@
       </c>
       <c r="E526" s="6" t="n">
         <v>12.9</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="5" t="inlineStr">
+        <is>
+          <t>מעדן לחתולים</t>
+        </is>
+      </c>
+      <c r="B527" s="5" t="inlineStr">
+        <is>
+          <t>חיות מחמד</t>
+        </is>
+      </c>
+      <c r="C527" s="5" t="inlineStr">
+        <is>
+          <t>Wet Cat Food / Pouch</t>
+        </is>
+      </c>
+      <c r="D527" s="5" t="inlineStr">
+        <is>
+          <t>Влажный корм для кошек</t>
+        </is>
+      </c>
+      <c r="E527" s="6" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="5" t="inlineStr">
+        <is>
+          <t>חטיפים לחתולים</t>
+        </is>
+      </c>
+      <c r="B528" s="5" t="inlineStr">
+        <is>
+          <t>חיות מחמד</t>
+        </is>
+      </c>
+      <c r="C528" s="5" t="inlineStr">
+        <is>
+          <t>Cat Treats</t>
+        </is>
+      </c>
+      <c r="D528" s="5" t="inlineStr">
+        <is>
+          <t>Лакомства для кошек</t>
+        </is>
+      </c>
+      <c r="E528" s="6" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="5" t="inlineStr">
+        <is>
+          <t>שימורים לכלבים</t>
+        </is>
+      </c>
+      <c r="B529" s="5" t="inlineStr">
+        <is>
+          <t>חיות מחמד</t>
+        </is>
+      </c>
+      <c r="C529" s="5" t="inlineStr">
+        <is>
+          <t>Canned Dog Food</t>
+        </is>
+      </c>
+      <c r="D529" s="5" t="inlineStr">
+        <is>
+          <t>Консервы для собак</t>
+        </is>
+      </c>
+      <c r="E529" s="6" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="5" t="inlineStr">
+        <is>
+          <t>חטיפים לכלבים</t>
+        </is>
+      </c>
+      <c r="B530" s="5" t="inlineStr">
+        <is>
+          <t>חיות מחמד</t>
+        </is>
+      </c>
+      <c r="C530" s="5" t="inlineStr">
+        <is>
+          <t>Dog Treats / Biscuits</t>
+        </is>
+      </c>
+      <c r="D530" s="5" t="inlineStr">
+        <is>
+          <t>Лакомства для собак</t>
+        </is>
+      </c>
+      <c r="E530" s="6" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="5" t="inlineStr">
+        <is>
+          <t>עצמות לעיסה לכלבים</t>
+        </is>
+      </c>
+      <c r="B531" s="5" t="inlineStr">
+        <is>
+          <t>חיות מחמד</t>
+        </is>
+      </c>
+      <c r="C531" s="5" t="inlineStr">
+        <is>
+          <t>Dog Chew Bones</t>
+        </is>
+      </c>
+      <c r="D531" s="5" t="inlineStr">
+        <is>
+          <t>Жевательные кости для собак</t>
+        </is>
+      </c>
+      <c r="E531" s="6" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="5" t="inlineStr">
+        <is>
+          <t>שקיות לאיסוף צרכים</t>
+        </is>
+      </c>
+      <c r="B532" s="5" t="inlineStr">
+        <is>
+          <t>חיות מחמד</t>
+        </is>
+      </c>
+      <c r="C532" s="5" t="inlineStr">
+        <is>
+          <t>Dog Waste Bags</t>
+        </is>
+      </c>
+      <c r="D532" s="5" t="inlineStr">
+        <is>
+          <t>Пакеты для уборки за собаками</t>
+        </is>
+      </c>
+      <c r="E532" s="6" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="5" t="inlineStr">
+        <is>
+          <t>שמפו לכלבים</t>
+        </is>
+      </c>
+      <c r="B533" s="5" t="inlineStr">
+        <is>
+          <t>חיות מחמד</t>
+        </is>
+      </c>
+      <c r="C533" s="5" t="inlineStr">
+        <is>
+          <t>Dog Shampoo</t>
+        </is>
+      </c>
+      <c r="D533" s="5" t="inlineStr">
+        <is>
+          <t>Шампунь для собак</t>
+        </is>
+      </c>
+      <c r="E533" s="6" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="5" t="inlineStr">
+        <is>
+          <t>פלמני בשר</t>
+        </is>
+      </c>
+      <c r="B534" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C534" s="5" t="inlineStr">
+        <is>
+          <t>Meat Pelmeni (Dumplings)</t>
+        </is>
+      </c>
+      <c r="D534" s="5" t="inlineStr">
+        <is>
+          <t>Пельмени с мясом</t>
+        </is>
+      </c>
+      <c r="E534" s="6" t="n">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="5" t="inlineStr">
+        <is>
+          <t>ורניקי תפוחי אדמה</t>
+        </is>
+      </c>
+      <c r="B535" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C535" s="5" t="inlineStr">
+        <is>
+          <t>Potato Vareniki</t>
+        </is>
+      </c>
+      <c r="D535" s="5" t="inlineStr">
+        <is>
+          <t>Вареники с картофелем</t>
+        </is>
+      </c>
+      <c r="E535" s="6" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="5" t="inlineStr">
+        <is>
+          <t>ורניקי דובדבנים</t>
+        </is>
+      </c>
+      <c r="B536" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C536" s="5" t="inlineStr">
+        <is>
+          <t>Cherry Vareniki</t>
+        </is>
+      </c>
+      <c r="D536" s="5" t="inlineStr">
+        <is>
+          <t>Вареники с вишней</t>
+        </is>
+      </c>
+      <c r="E536" s="6" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="5" t="inlineStr">
+        <is>
+          <t>גבינת טוורוג</t>
+        </is>
+      </c>
+      <c r="B537" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C537" s="5" t="inlineStr">
+        <is>
+          <t>Tvorog Curd Cheese</t>
+        </is>
+      </c>
+      <c r="D537" s="5" t="inlineStr">
+        <is>
+          <t>Творог</t>
+        </is>
+      </c>
+      <c r="E537" s="6" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="5" t="inlineStr">
+        <is>
+          <t>סירניקי</t>
+        </is>
+      </c>
+      <c r="B538" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C538" s="5" t="inlineStr">
+        <is>
+          <t>Syrniki (Curd Pancakes)</t>
+        </is>
+      </c>
+      <c r="D538" s="5" t="inlineStr">
+        <is>
+          <t>Сырники</t>
+        </is>
+      </c>
+      <c r="E538" s="6" t="n">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="5" t="inlineStr">
+        <is>
+          <t>חלב מרוכז (סגושצ'ונקה)</t>
+        </is>
+      </c>
+      <c r="B539" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C539" s="5" t="inlineStr">
+        <is>
+          <t>Condensed Milk (Sgushchyonka)</t>
+        </is>
+      </c>
+      <c r="D539" s="5" t="inlineStr">
+        <is>
+          <t>Сгущенное молоко</t>
+        </is>
+      </c>
+      <c r="E539" s="6" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="5" t="inlineStr">
+        <is>
+          <t>שפרוטים בשמן</t>
+        </is>
+      </c>
+      <c r="B540" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C540" s="5" t="inlineStr">
+        <is>
+          <t>Smoked Sprats in Oil</t>
+        </is>
+      </c>
+      <c r="D540" s="5" t="inlineStr">
+        <is>
+          <t>Шпроты в масле</t>
+        </is>
+      </c>
+      <c r="E540" s="6" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="5" t="inlineStr">
+        <is>
+          <t>נקניק דוקטורסקיה</t>
+        </is>
+      </c>
+      <c r="B541" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C541" s="5" t="inlineStr">
+        <is>
+          <t>Doktorskaya Bologna Sausage</t>
+        </is>
+      </c>
+      <c r="D541" s="5" t="inlineStr">
+        <is>
+          <t>Докторская колбаса</t>
+        </is>
+      </c>
+      <c r="E541" s="6" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="5" t="inlineStr">
+        <is>
+          <t>דג הרינג (מטיאס)</t>
+        </is>
+      </c>
+      <c r="B542" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C542" s="5" t="inlineStr">
+        <is>
+          <t>Pickled Herring / Matias</t>
+        </is>
+      </c>
+      <c r="D542" s="5" t="inlineStr">
+        <is>
+          <t>Сельдь / Матиас</t>
+        </is>
+      </c>
+      <c r="E542" s="6" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="5" t="inlineStr">
+        <is>
+          <t>איקרה אדומה (קוויאר)</t>
+        </is>
+      </c>
+      <c r="B543" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C543" s="5" t="inlineStr">
+        <is>
+          <t>Red Caviar (Salmon Roe)</t>
+        </is>
+      </c>
+      <c r="D543" s="5" t="inlineStr">
+        <is>
+          <t>Красная икра</t>
+        </is>
+      </c>
+      <c r="E543" s="6" t="n">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="5" t="inlineStr">
+        <is>
+          <t>קבאס</t>
+        </is>
+      </c>
+      <c r="B544" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C544" s="5" t="inlineStr">
+        <is>
+          <t>Kvass (Fermented Bread Drink)</t>
+        </is>
+      </c>
+      <c r="D544" s="5" t="inlineStr">
+        <is>
+          <t>Квас</t>
+        </is>
+      </c>
+      <c r="E544" s="6" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="5" t="inlineStr">
+        <is>
+          <t>לחם בורודינסקי</t>
+        </is>
+      </c>
+      <c r="B545" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C545" s="5" t="inlineStr">
+        <is>
+          <t>Borodinsky Dark Rye Bread</t>
+        </is>
+      </c>
+      <c r="D545" s="5" t="inlineStr">
+        <is>
+          <t>Бородинский хлеб</t>
+        </is>
+      </c>
+      <c r="E545" s="6" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="5" t="inlineStr">
+        <is>
+          <t>חטיף גבינה מצופה (סירק)</t>
+        </is>
+      </c>
+      <c r="B546" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C546" s="5" t="inlineStr">
+        <is>
+          <t>Glazed Curd Bar (Sirok)</t>
+        </is>
+      </c>
+      <c r="D546" s="5" t="inlineStr">
+        <is>
+          <t>Глазированный сырок</t>
+        </is>
+      </c>
+      <c r="E546" s="6" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="5" t="inlineStr">
+        <is>
+          <t>מלפפונים מלוחים קלות</t>
+        </is>
+      </c>
+      <c r="B547" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C547" s="5" t="inlineStr">
+        <is>
+          <t>Lightly Salted Pickles (Malosolnye)</t>
+        </is>
+      </c>
+      <c r="D547" s="5" t="inlineStr">
+        <is>
+          <t>Малосольные огурцы</t>
+        </is>
+      </c>
+      <c r="E547" s="6" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="5" t="inlineStr">
+        <is>
+          <t>חזרת אדומה (חריין)</t>
+        </is>
+      </c>
+      <c r="B548" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C548" s="5" t="inlineStr">
+        <is>
+          <t>Horseradish with Beets (Khren)</t>
+        </is>
+      </c>
+      <c r="D548" s="5" t="inlineStr">
+        <is>
+          <t>Хрен со свеклой</t>
+        </is>
+      </c>
+      <c r="E548" s="6" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="5" t="inlineStr">
+        <is>
+          <t>חמאת וולוגדה</t>
+        </is>
+      </c>
+      <c r="B549" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C549" s="5" t="inlineStr">
+        <is>
+          <t>Vologda Cultured Butter</t>
+        </is>
+      </c>
+      <c r="D549" s="5" t="inlineStr">
+        <is>
+          <t>Вологодское масло</t>
+        </is>
+      </c>
+      <c r="E549" s="6" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="5" t="inlineStr">
+        <is>
+          <t>שוקולד אליונקה</t>
+        </is>
+      </c>
+      <c r="B550" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C550" s="5" t="inlineStr">
+        <is>
+          <t>Alenka Milk Chocolate</t>
+        </is>
+      </c>
+      <c r="D550" s="5" t="inlineStr">
+        <is>
+          <t>Шоколад Алёнка</t>
+        </is>
+      </c>
+      <c r="E550" s="6" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="5" t="inlineStr">
+        <is>
+          <t>ביצי שליו</t>
+        </is>
+      </c>
+      <c r="B551" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C551" s="5" t="inlineStr">
+        <is>
+          <t>Quail Eggs</t>
+        </is>
+      </c>
+      <c r="D551" s="5" t="inlineStr">
+        <is>
+          <t>Перепелиные яйца</t>
+        </is>
+      </c>
+      <c r="E551" s="6" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="5" t="inlineStr">
+        <is>
+          <t>חלווה חמניות</t>
+        </is>
+      </c>
+      <c r="B552" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C552" s="5" t="inlineStr">
+        <is>
+          <t>Sunflower Seed Halva</t>
+        </is>
+      </c>
+      <c r="D552" s="5" t="inlineStr">
+        <is>
+          <t>Подсолнечная халва</t>
+        </is>
+      </c>
+      <c r="E552" s="6" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="5" t="inlineStr">
+        <is>
+          <t>פסטילא (מרמלדה רוסית)</t>
+        </is>
+      </c>
+      <c r="B553" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C553" s="5" t="inlineStr">
+        <is>
+          <t>Pastila Fruit Marshmallow</t>
+        </is>
+      </c>
+      <c r="D553" s="5" t="inlineStr">
+        <is>
+          <t>Пастила</t>
+        </is>
+      </c>
+      <c r="E553" s="6" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="5" t="inlineStr">
+        <is>
+          <t>משקה מורס (חמוציות)</t>
+        </is>
+      </c>
+      <c r="B554" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C554" s="5" t="inlineStr">
+        <is>
+          <t>Cranberry Mors Drink</t>
+        </is>
+      </c>
+      <c r="D554" s="5" t="inlineStr">
+        <is>
+          <t>Клюквенный морс</t>
+        </is>
+      </c>
+      <c r="E554" s="6" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="5" t="inlineStr">
+        <is>
+          <t>עוגיות פריאניקי</t>
+        </is>
+      </c>
+      <c r="B555" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C555" s="5" t="inlineStr">
+        <is>
+          <t>Pryaniki Spiced Honey Cookies</t>
+        </is>
+      </c>
+      <c r="D555" s="5" t="inlineStr">
+        <is>
+          <t>Пряники</t>
+        </is>
+      </c>
+      <c r="E555" s="6" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="5" t="inlineStr">
+        <is>
+          <t>סושיקי / בובליקי</t>
+        </is>
+      </c>
+      <c r="B556" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C556" s="5" t="inlineStr">
+        <is>
+          <t>Sushki Tea Rings</t>
+        </is>
+      </c>
+      <c r="D556" s="5" t="inlineStr">
+        <is>
+          <t>Сушки</t>
+        </is>
+      </c>
+      <c r="E556" s="6" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="5" t="inlineStr">
+        <is>
+          <t>מקרל מעושן (סקומבריה)</t>
+        </is>
+      </c>
+      <c r="B557" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C557" s="5" t="inlineStr">
+        <is>
+          <t>Cold Smoked Mackerel (Skumbriya)</t>
+        </is>
+      </c>
+      <c r="D557" s="5" t="inlineStr">
+        <is>
+          <t>Скумбрия копченая</t>
+        </is>
+      </c>
+      <c r="E557" s="6" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="5" t="inlineStr">
+        <is>
+          <t>שמנת חמוצה סמטנה</t>
+        </is>
+      </c>
+      <c r="B558" s="5" t="inlineStr">
+        <is>
+          <t>מעדניה רוסית</t>
+        </is>
+      </c>
+      <c r="C558" s="5" t="inlineStr">
+        <is>
+          <t>Smetana Russian Sour Cream</t>
+        </is>
+      </c>
+      <c r="D558" s="5" t="inlineStr">
+        <is>
+          <t>Сметана</t>
+        </is>
+      </c>
+      <c r="E558" s="6" t="n">
+        <v>9.9</v>
       </c>
     </row>
   </sheetData>
